--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/01_CHUAN_IMPORT_QUIZIZZ_QUIZ_COM_904_CAU/Day_04_System Prompt Engineering _ Tool Calling Engine/Day_04_Phan_02_19_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/01_CHUAN_IMPORT_QUIZIZZ_QUIZ_COM_904_CAU/Day_04_System Prompt Engineering _ Tool Calling Engine/Day_04_Phan_02_19_Cau.xlsx
@@ -748,7 +748,7 @@
       </c>
       <c r="G5" s="3" t="n"/>
       <c r="H5" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5" s="4" t="n">
         <v>60</v>
@@ -756,7 +756,7 @@
       <c r="J5" s="3" t="n"/>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tách thông tin định danh do người dùng cung cấp khỏi bằng chứng thay đổi theo thời gian cần truy xuất.</t>
+          <t>Người dùng đã cung cấp đủ mã chuyến bay và ngày bay, và câu trả lời bắt buộc phải dựa trên dữ liệu mới nhất từ công cụ; chính sách tool-choice đúng là bắt buộc dùng `flight_status` (forced tool-choice).</t>
         </is>
       </c>
     </row>
@@ -911,7 +911,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,4,5</t>
         </is>
       </c>
       <c r="I8" s="4" t="n">
@@ -920,7 +920,7 @@
       <c r="J8" s="3" t="n"/>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đừng dựa vào động từ HTTP hay tên hàm; hãy đọc tác động được mô tả.</t>
+          <t>Các lời gọi làm thay đổi trạng thái bên ngoài (state-modifying): `GET /report?mark_seen=true` thay đổi trạng thái đã xem trên server (a), `send_email` gửi email thật ra ngoài (d), và `reserve_room(hold=true)` tạo bản ghi giữ phòng tạm (e). `search_docs` và `preview_email` là thao tác chỉ đọc/cục bộ.</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="G9" s="3" t="n"/>
       <c r="H9" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I9" s="4" t="n">
         <v>60</v>
@@ -968,7 +968,7 @@
       <c r="J9" s="3" t="n"/>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Hãy xét cả các đối số mặc định trước khi phân loại.</t>
+          <t>Hàm `check_coupon(code, apply=True)` có đối số mặc định `apply=True` làm thay đổi giỏ hàng phía máy chủ, nên lời gọi này là một hành động ghi dữ liệu (write action).</t>
         </is>
       </c>
     </row>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="G11" s="3" t="n"/>
       <c r="H11" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I11" s="4" t="n">
         <v>60</v>
@@ -1075,7 +1075,7 @@
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Phân biệt không nhận được phản hồi với việc không có tác động nào xảy ra.</t>
+          <t>Khi `charge_card` bị timeout, cổng thanh toán có thể đã trừ tiền. Nếu client tạo request ID mới để thử lại thì có nguy cơ trừ tiền hai lần; cách sửa đúng là đối soát giao dịch và dùng lại đúng idempotency key ban đầu.</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="G14" s="3" t="n"/>
       <c r="H14" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I14" s="4" t="n">
         <v>60</v>
@@ -1229,7 +1229,7 @@
       <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Hãy kiểm tra state nào cần còn lại sau phần cập nhật của node.</t>
+          <t>Trong LangGraph, để các `ToolMessage` được thêm nối tiếp vào danh sách lịch sử thay vì ghi đè toàn bộ danh sách, khai báo đúng trong TypedDict là `messages: Annotated[list, add_messages]`.</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="G15" s="3" t="n"/>
       <c r="H15" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I15" s="4" t="n">
         <v>60</v>
@@ -1278,7 +1278,7 @@
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Các key trả về phải là key của State, còn value phải đúng ngữ nghĩa cập nhật.</t>
+          <t>Node trong LangGraph trả về dictionary chứa các key cập nhật state: `return {'messages':[response], 'attempts': state['attempts']+1}` cập nhật cả messages thông qua reducer và tăng số lần thử attempts.</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="G16" s="3" t="n"/>
       <c r="H16" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I16" s="4" t="n">
         <v>60</v>
@@ -1326,7 +1326,7 @@
       <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tách nơi quyết định hành động khỏi nơi tạo quan sát bên ngoài.</t>
+          <t>Trong thiết kế đồ thị chuẩn của LangGraph, node `agent` chỉ đưa ra quyết định gọi tool, còn việc thực thi tool phải được tách riêng thành node `tools` riêng biệt để quan sát và quản lý trạng thái độc lập.</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="G17" s="3" t="n"/>
       <c r="H17" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I17" s="4" t="n">
         <v>60</v>
@@ -1375,7 +1375,7 @@
       <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Áp đúng điều kiện đã cho lên message cuối.</t>
+          <t>Router kiểm tra `if last.tool_calls: return 'tools' else: return 'END'`. Với AIMessage có `tool_calls` không rỗng, đích đến bắt buộc là node `tools` bất kể text có rỗng hay không.</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>o1 → o2 → o3 → o4 → o5</t>
+          <t>o2 → o3 → o4 → o1 → o5</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -1428,7 +1428,7 @@
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Mọi đích của edge phải tồn tại trước bước kiểm tra/compile.</t>
+          <t>Quy trình lắp ghép đồ thị LangGraph: Khởi tạo `StateGraph(State)` (o2) -&gt; Đăng ký các node `agent` và `tools` (o3) -&gt; Thêm edge START→agent (o4) -&gt; Thêm conditional edge agent→tools/END và normal edge tools→agent (o1) -&gt; Compile builder (o5).</t>
         </is>
       </c>
     </row>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="G19" s="3" t="n"/>
       <c r="H19" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I19" s="4" t="n">
         <v>60</v>
@@ -1477,7 +1477,7 @@
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Lần theo tình huống có tool call, từng edge một.</t>
+          <t>Nếu graph có edge conditional agent→tools nhưng thiếu edge đi ra khỏi node `tools`, khi nhánh tool thực thi xong thì đồ thị sẽ dừng lại mà không quay trở về `agent` để sinh kết quả cuối cùng.</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="G20" s="3" t="n"/>
       <c r="H20" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I20" s="4" t="n">
         <v>60</v>
@@ -1527,7 +1527,7 @@
       <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: So danh sách tên node đã đăng ký với mọi đích đến.</t>
+          <t>Router ánh xạ tới `tool_node` nhưng node được đăng ký là `tools`, khiến compiler báo lỗi node đích không tồn tại. Cách sửa nhỏ nhất là đổi tên ánh xạ đích trong router thành node đã đăng ký là `tools`.</t>
         </is>
       </c>
     </row>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>o1 → o2 → o3 → o4</t>
+          <t>o3 → o2 → o1 → o4</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -1582,7 +1582,7 @@
       <c r="J21" s="3" t="n"/>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Dùng nơi tạo ra từng message để dựng đường đi.</t>
+          <t>Đường đi logic qua đồ thị: agent yêu cầu tool (o3) -&gt; tools thực thi tạo Observation (o2) -&gt; agent nhận Observation tạo final answer (o1) -&gt; kết thúc END (o4).</t>
         </is>
       </c>
     </row>
